--- a/site/exports/nju-history-chinese.xlsx
+++ b/site/exports/nju-history-chinese.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="32.2" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -728,13 +728,67 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>于磊</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>中国历史系</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>https://history.nju.edu.cn/yl/main.htm</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Current employment/directory unknown.；Own mentors unknown.；All study degree conferrals unknown.；Kyushu 研究生 stage not forcibly mapped to master or nondegree.；Selected works are translations, not authored monographs; publisher metadata unverified.；来源单位：历史学院中国历史系。本站按“中国历史系”归组仅供展示，保留原单位标签；不据此认证法律行政层级、校区或当前任职。</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K5"/>
+  <autoFilter ref="A1:K6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -746,13 +800,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="46.2" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="19.6" customWidth="1" min="4" max="4"/>
+    <col width="32.2" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -828,7 +882,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1925,8 +1979,398 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>于磊</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>study_period</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>博士研究生</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>日本九州大学人文科学府</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2010-10</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2013-12</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>东洋史</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Study labels do not establish conferral. Japanese 2009-2010 研究生 retained without mapping to master/doctor or assuming degree/nondegree.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>https://history.nju.edu.cn/yl/main.htm</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>于磊</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>study_period</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>研究生</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>日本九州大学人文科学府</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2010-09</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>东洋史</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Study labels do not establish conferral. Japanese 2009-2010 研究生 retained without mapping to master/doctor or assuming degree/nondegree.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>https://history.nju.edu.cn/yl/main.htm</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>于磊</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>study_period</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>硕士研究生</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>南京大学历史学系元史研究室/民族与边疆研究中心</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2005-09</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2008-06</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Study labels do not establish conferral. Japanese 2009-2010 研究生 retained without mapping to master/doctor or assuming degree/nondegree.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>https://history.nju.edu.cn/yl/main.htm</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>于磊</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>study_period</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>山东烟台大学中文系</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2001-09</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2005-06</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>汉语言文学</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Study labels do not establish conferral. Japanese 2009-2010 研究生 retained without mapping to master/doctor or assuming degree/nondegree.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>https://history.nju.edu.cn/yl/main.htm</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>于磊</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>南京大学历史学院</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源role_as_source：副教授；来源institution_as_source：南京大学历史学院；来源记载（period_end_note）：source open-ended dash, not independent current employment verification</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>https://history.nju.edu.cn/yl/main.htm</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>于磊</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>助理研究员</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>南京大学历史学院</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2013-12</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源role_as_source：助理研究员；来源institution_as_source：南京大学历史学院</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>https://history.nju.edu.cn/yl/main.htm</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S19"/>
+  <autoFilter ref="A1:S25"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -1947,6 +2391,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2106,7 +2556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2557,8 +3007,112 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>于磊</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>元代江南政治社会史研究</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>https://history.nju.edu.cn/yl/main.htm</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>translated_book</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>https://history.nju.edu.cn/yl/main.htm</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：植松正；来源translators_as_source：于磊；来源person_contribution_role_as_source：translator；来源书目信息（month_as_source）：12</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>于磊</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>元代知识人与地域社会</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>https://history.nju.edu.cn/yl/main.htm</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>translated_book</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>https://history.nju.edu.cn/yl/main.htm</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：森田宪司；来源translators_as_source：于磊；来源person_contribution_role_as_source：translator；来源书目信息（month_as_source）：5</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L9"/>
+  <autoFilter ref="A1:L11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -2572,6 +3126,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2583,14 +3141,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -3142,8 +3700,45 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>于磊</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-nju-yulei-history-s001-d69fc142a6d7</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>https://history.nju.edu.cn/yl/main.htm</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:17:27Z</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>nju</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>南京大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G15"/>
+  <autoFilter ref="A1:G16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
@@ -3159,6 +3754,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
